--- a/data/trans_dic/P32D_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,79</t>
+          <t>0,38; 5,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 10,52</t>
+          <t>0,37; 8,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,65</t>
+          <t>0,82; 4,96</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,67</t>
+          <t>1,56; 7,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,47</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,39</t>
+          <t>1,47; 6,15</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 13,24</t>
+          <t>4,79; 13,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,85</t>
+          <t>3,26; 8,98</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 13,69</t>
+          <t>2,51; 13,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 14,98</t>
+          <t>4,15; 15,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 11,64</t>
+          <t>4,08; 12,33</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 23,36</t>
+          <t>2,07; 22,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,15</t>
+          <t>0,0; 25,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 20,52</t>
+          <t>2,43; 19,53</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 23,73</t>
+          <t>11,6; 23,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,49; 13,63</t>
+          <t>3,07; 12,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,66; 18,34</t>
+          <t>9,69; 17,57</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 14,98</t>
+          <t>7,32; 15,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,65</t>
+          <t>0,73; 9,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 10,51</t>
+          <t>2,73; 10,58</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,11; 20,43</t>
+          <t>11,13; 20,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,21; 23,56</t>
+          <t>10,58; 24,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,17; 19,68</t>
+          <t>12,11; 19,77</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,81; 10,89</t>
+          <t>7,78; 10,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,49</t>
+          <t>2,69; 7,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,91</t>
+          <t>5,67; 8,93</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>690; 8610</t>
+          <t>689; 9513</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>359; 9542</t>
+          <t>336; 8135</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1826; 12571</t>
+          <t>2211; 13425</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3772; 19619</t>
+          <t>3998; 20296</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7564</t>
+          <t>0; 6703</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5328; 23825</t>
+          <t>5478; 22902</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8607; 24208</t>
+          <t>8767; 24380</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 5920</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9094; 24136</t>
+          <t>8894; 24483</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4446; 24184</t>
+          <t>4430; 24389</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4987; 18522</t>
+          <t>5133; 18753</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12838; 34971</t>
+          <t>12256; 37027</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>613; 7275</t>
+          <t>644; 7057</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2416</t>
+          <t>0; 2160</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>922; 8152</t>
+          <t>964; 7757</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19012; 39159</t>
+          <t>19147; 39350</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3368; 13141</t>
+          <t>2959; 12400</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25263; 47963</t>
+          <t>25328; 45935</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22874; 45527</t>
+          <t>22239; 45821</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3579; 38447</t>
+          <t>2896; 36422</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17273; 73847</t>
+          <t>19198; 74298</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30649; 56363</t>
+          <t>30694; 57381</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10188; 23520</t>
+          <t>10557; 24603</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45728; 73927</t>
+          <t>45486; 74283</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>122651; 171136</t>
+          <t>122231; 171466</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28096; 76684</t>
+          <t>27570; 76004</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>149926; 231208</t>
+          <t>147196; 231696</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32D_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,29</t>
+          <t>0,43; 4,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,97</t>
+          <t>0,98; 8,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,96</t>
+          <t>1,0; 4,67</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,94</t>
+          <t>1,71; 7,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,15</t>
+          <t>1,56; 5,86</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 13,33</t>
+          <t>5,08; 13,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 8,98</t>
+          <t>3,67; 9,32</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 13,8</t>
+          <t>2,31; 14,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 15,17</t>
+          <t>4,16; 15,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,33</t>
+          <t>3,92; 11,65</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 22,66</t>
+          <t>1,95; 21,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,16</t>
+          <t>0,0; 24,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 19,53</t>
+          <t>2,86; 19,42</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,6; 23,84</t>
+          <t>11,68; 22,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,07; 12,86</t>
+          <t>3,62; 13,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,69; 17,57</t>
+          <t>9,51; 17,33</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,08</t>
+          <t>9,19; 18,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 9,14</t>
+          <t>5,0; 13,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 10,58</t>
+          <t>8,18; 14,36</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,13; 20,8</t>
+          <t>10,91; 19,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,58; 24,65</t>
+          <t>10,28; 24,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,11; 19,77</t>
+          <t>11,9; 19,51</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,78; 10,91</t>
+          <t>8,12; 11,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,42</t>
+          <t>5,63; 9,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,93</t>
+          <t>7,65; 10,07</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6437</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>689; 9513</t>
+          <t>725; 8012</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>336; 8135</t>
+          <t>953; 8438</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2211; 13425</t>
+          <t>2660; 12469</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>11797</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3998; 20296</t>
+          <t>4442; 20414</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6703</t>
+          <t>0; 6815</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5478; 22902</t>
+          <t>5962; 22422</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>17178</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8767; 24380</t>
+          <t>9414; 25145</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5920</t>
+          <t>0; 4764</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8894; 24483</t>
+          <t>10065; 25533</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>23423</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4430; 24389</t>
+          <t>4671; 29259</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5133; 18753</t>
+          <t>5731; 21398</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12256; 37027</t>
+          <t>13295; 39544</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>849</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3613</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>644; 7057</t>
+          <t>664; 7276</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2160</t>
+          <t>0; 2604</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>964; 7757</t>
+          <t>1286; 8737</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34495</t>
+          <t>34425</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19147; 39350</t>
+          <t>19031; 37261</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2959; 12400</t>
+          <t>3552; 13554</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25328; 45935</t>
+          <t>24829; 45249</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>43913</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48246</t>
+          <t>63560</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22239; 45821</t>
+          <t>31808; 62423</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2896; 36422</t>
+          <t>11693; 31512</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19198; 74298</t>
+          <t>47423; 83241</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>46764</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>18473</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58058</t>
+          <t>65236</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30694; 57381</t>
+          <t>34083; 62396</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10557; 24603</t>
+          <t>11822; 28061</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45486; 74283</t>
+          <t>50863; 83395</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>161482</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>54715</t>
+          <t>64186</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>198824</t>
+          <t>225668</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>122231; 171466</t>
+          <t>135843; 191270</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>27570; 76004</t>
+          <t>50900; 82942</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>147196; 231696</t>
+          <t>197117; 259529</t>
         </is>
       </c>
     </row>
